--- a/artfynd/A 56863-2024 artfynd.xlsx
+++ b/artfynd/A 56863-2024 artfynd.xlsx
@@ -38989,7 +38989,7 @@
         <v>136017887</v>
       </c>
       <c r="B330" t="n">
-        <v>100046</v>
+        <v>100049</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>

--- a/artfynd/A 56863-2024 artfynd.xlsx
+++ b/artfynd/A 56863-2024 artfynd.xlsx
@@ -38989,7 +38989,7 @@
         <v>136017887</v>
       </c>
       <c r="B330" t="n">
-        <v>100049</v>
+        <v>100050</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>

--- a/artfynd/A 56863-2024 artfynd.xlsx
+++ b/artfynd/A 56863-2024 artfynd.xlsx
@@ -21720,7 +21720,7 @@
         <v>136017921</v>
       </c>
       <c r="B183" t="n">
-        <v>57847</v>
+        <v>57849</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -23132,7 +23132,7 @@
         <v>136187334</v>
       </c>
       <c r="B194" t="n">
-        <v>61562</v>
+        <v>61564</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>

--- a/artfynd/A 56863-2024 artfynd.xlsx
+++ b/artfynd/A 56863-2024 artfynd.xlsx
@@ -18759,7 +18759,7 @@
         <v>128813379</v>
       </c>
       <c r="B158" t="n">
-        <v>93490</v>
+        <v>93492</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>

--- a/artfynd/A 56863-2024 artfynd.xlsx
+++ b/artfynd/A 56863-2024 artfynd.xlsx
@@ -18759,7 +18759,7 @@
         <v>128813379</v>
       </c>
       <c r="B158" t="n">
-        <v>93492</v>
+        <v>93498</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>

--- a/artfynd/A 56863-2024 artfynd.xlsx
+++ b/artfynd/A 56863-2024 artfynd.xlsx
@@ -18759,7 +18759,7 @@
         <v>128813379</v>
       </c>
       <c r="B158" t="n">
-        <v>93498</v>
+        <v>93510</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>

--- a/artfynd/A 56863-2024 artfynd.xlsx
+++ b/artfynd/A 56863-2024 artfynd.xlsx
@@ -18759,7 +18759,7 @@
         <v>128813379</v>
       </c>
       <c r="B158" t="n">
-        <v>93510</v>
+        <v>93511</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>

--- a/artfynd/A 56863-2024 artfynd.xlsx
+++ b/artfynd/A 56863-2024 artfynd.xlsx
@@ -18759,7 +18759,7 @@
         <v>128813379</v>
       </c>
       <c r="B158" t="n">
-        <v>93511</v>
+        <v>93514</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>

--- a/artfynd/A 56863-2024 artfynd.xlsx
+++ b/artfynd/A 56863-2024 artfynd.xlsx
@@ -18759,7 +18759,7 @@
         <v>128813379</v>
       </c>
       <c r="B158" t="n">
-        <v>93514</v>
+        <v>93518</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
